--- a/docs/채용현황판_프로젝트_정리.xlsx
+++ b/docs/채용현황판_프로젝트_정리.xlsx
@@ -9,12 +9,13 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="한눈에 보기" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="진행 경과" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HR 관리자 사용법" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="현업 담당자 사용법" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="엑셀 규칙과 반영 규칙" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="설정과 보안" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="문제 해결" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="남은 일" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="작업 기록" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HR 관리자 사용법" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="현업 담당자 사용법" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="엑셀 규칙과 반영 규칙" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="설정과 보안" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="문제 해결" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="남은 일" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -435,17 +436,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
     <col width="100" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>항목</t>
+          <t>번호</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -457,96 +460,144 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>운영 사이트</t>
+          <t>설명</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>https://d12l-hana06.vercel.app</t>
+          <t>채용 백데이터 엑셀을 반영해서, HR 관리자는 전체 공고와 열람 권한을 관리하고 현업 담당자는 승인받은 공고의 진행 단계만 보는 웹 현황판입니다.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>설정 점검</t>
+          <t>항목</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>/api/health ("저장소":"정상"이면 OK)</t>
+          <t>내용</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>코드</t>
+          <t>운영 사이트</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>GitHub seonhye061vv/- (main 브랜치)</t>
+          <t>https://d12l-hana06.vercel.app</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>배포</t>
+          <t>설정 점검</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Vercel. main에 올라가면 자동 배포</t>
+          <t>https://d12l-hana06.vercel.app/api/health ("저장소":"정상"이면 OK)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>데이터</t>
+          <t>코드</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Upstash Redis (도쿄, 무료 요금제)</t>
+          <t>GitHub 공개 저장소 seonhye061vv/- (main). 올리면 Vercel이 자동 배포</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>기획서</t>
+          <t>데이터</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>recruitment_dashboard_PRD.xlsx</t>
+          <t>Upstash Redis (도쿄, 무료)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>설명</t>
+          <t>관리자 로그인</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>채용 백데이터 엑셀을 반영해서, HR 관리자는 전체 공고를 관리하고 현업 담당자는 승인받은 공고의 진행 단계만 보는 웹 현황판입니다.</t>
+          <t>admin / 비밀번호는 Vercel 환경 변수 ADMIN_PASSWORD</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>평가용 테스트 관리자</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>test_admin / 비밀번호는 Vercel 환경 변수 TEST_ADMIN_PASSWORD</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>최신 백데이터</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>채용현황판 백데이터_v.3.xlsx (공고 9건, 권한부여대상자 25개 부서·29명)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>기획서</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>recruitment_dashboard_PRD.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>데모 미리보기</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>https://claude.ai/artifact/Ng8kQ1GuCdhQwXbhM6DoUu (예시 데이터)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>현재 상태: 사이트 접속, 관리자 로그인, 저장소 연결까지 정상입니다. 실제 명단 등록과 대상자별 승인은 아직 하지 않았습니다.</t>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>현재 상태(2026-10-14 17:30 기준): 사이트 접속·관리자 로그인·저장소 연결 정상. 화면 디자인·모션·사용 편의 기능 반영 완료. 실제 명단(v.3) 업로드와 대상자별 연결·승인은 사용자가 진행할 차례.</t>
         </is>
       </c>
     </row>
@@ -561,11 +612,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
     <col width="100" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -588,7 +641,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>기획서(PRD) 기준으로 관리자 화면과 현업 화면을 만들고 예시 데이터로 데모를 공유했습니다.</t>
+          <t>기획서(PRD) 기준으로 HR 관리자 화면과 현업 화면을 만들고 예시 데이터 데모를 공유했습니다.</t>
         </is>
       </c>
     </row>
@@ -600,7 +653,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>현업 로그인을 이메일 + 비밀번호로 정하고, 임시 비밀번호가 자동 발급되도록 했습니다. 첫 로그인 때 본인 비밀번호로 바꿔야 합니다.</t>
+          <t>회사가 M365·Google Workspace를 쓰지 않아, 윈도우 PC 폴더의 엑셀을 PC 프로그램이 서버로 보내는 방식으로 정했습니다(기본 1시간, 5분 단위 변경).</t>
         </is>
       </c>
     </row>
@@ -612,7 +665,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>완료 공고는 모든 단계가 끝난 뒤 7일이 지나면 현업 화면에서 숨기도록 기본값을 정했습니다.</t>
+          <t>현업 로그인은 이메일 + 비밀번호. 관리자가 이메일을 연결하면 임시 비밀번호가 자동 발급되고, 첫 로그인 때 본인 비밀번호로 바꿔야 합니다.</t>
         </is>
       </c>
     </row>
@@ -624,7 +677,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>권한부여대상자 명단 파일(본부·부서·권한부여대상자N·이메일)을 따로 올릴 수 있게 했고, 명단 오타 두 곳을 고친 파일을 만들었습니다.</t>
+          <t>완료 공고는 모든 단계가 끝나고 7일이 지나면 현업 화면에서 숨깁니다(관리자가 기간 변경 가능).</t>
         </is>
       </c>
     </row>
@@ -636,7 +689,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>처음 배포 후 서버 연결 오류가 나서 점검 페이지(/api/health)를 추가해 저장소 미연결을 확인했습니다.</t>
+          <t>권한부여대상자 명단(본부·부서·대상자·이메일)을 따로 올릴 수 있게 했습니다.</t>
         </is>
       </c>
     </row>
@@ -648,7 +701,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Vercel의 Upstash 연동 페이지가 404여서 Upstash에서 DB를 직접 만들고 주소와 토큰을 Vercel 환경 변수에 넣은 뒤 재배포해 정상 접속을 확인했습니다.</t>
+          <t>Vercel 배포 후 '서버에 연결할 수 없습니다' 오류 → 점검 페이지(/api/health)로 저장소 미연결을 확인 → Upstash에서 DB를 직접 만들고 주소·토큰을 환경 변수에 넣어 해결했습니다.</t>
         </is>
       </c>
     </row>
@@ -660,7 +713,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>참고 이미지(PinHome)를 기준으로 청록 사이드바 + 흰 카드 디자인으로 바꿨습니다.</t>
+          <t>PinHome 참고 이미지로 청록 사이드바 + 흰 카드 디자인, 로그인 첫 화면을 개편했습니다.</t>
         </is>
       </c>
     </row>
@@ -672,7 +725,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>HR 관리자가 '현업 화면 보기'에서 대상자별 현업 화면을 볼 수 있게 했습니다(연결 전인 사람도 선택 가능).</t>
+          <t>HR 관리자 메뉴 '현업 화면 보기'로 대상자별 현업 화면을 그대로 확인할 수 있게 했습니다.</t>
         </is>
       </c>
     </row>
@@ -684,7 +737,67 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>'열람 권한' 탭의 이메일 칸을 넓혀 관리자가 직접 고치기 쉽게 했습니다.</t>
+          <t>공개용 정리 문서(워드·엑셀)를 GitHub docs 폴더에, 실명이 들어간 개인 보관용 파일을 프로젝트 파일에 저장했습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>화면 모션을 넣었다가 '과하다'는 의견으로 줄였습니다. 최종: 화면 등장 효과, 막대 차오름, 숫자 카운트업, 마우스 반응, 로그인 말풍선 흔들림, 진행 중 점 퍼짐, 현재 단계 말풍선 안쪽 점 박동(바깥 빛은 제거).</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>평가용 테스트 관리자 test_admin을 추가했습니다(환경 변수 TEST_ADMIN_PASSWORD가 있을 때만 로그인).</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>사용 편의 6가지: 일괄 연결·승인, 임시 비밀번호 엑셀 내려받기, 9단계 표를 진행 막대로 정리, 그래프 막대 눌러 거르기, 'N/9단계 처리' 진행률, 로그인 편의(비밀번호 보기·이메일 기억·분실 안내). 휴대폰 화면 가로 넘침도 고쳤습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>명단에 없는 사람을 '대상자 직접 추가'로 등록할 수 있게 했습니다(명단을 다시 올려도 유지, 삭제 가능).</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>백데이터 v.3을 확인했습니다. 오류 없음, 공고 9건. 리스크관리부·소비자보호부 공고는 명단에 같은 부서가 없어 후보 0명입니다.</t>
         </is>
       </c>
     </row>
@@ -699,17 +812,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
     <col width="100" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>번호</t>
+          <t>시각(한국)</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -721,108 +836,336 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10-14 11:07 · d5ad083</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>로그인: 이메일 칸에 admin, 비밀번호 칸에 Vercel 환경 변수 ADMIN_PASSWORD 값</t>
+          <t>저장소 생성</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10-14 11:41 · 9ed9363</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>현황판: 전체 공고와 단계별 진행 상태. 표시 기간이 지난 완료 공고도 관리자에게는 보임</t>
+          <t>현황판 첫 미리보기(MVP) 추가</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10-14 11:48 · 892403d</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>엑셀 반영: 엑셀을 올리면 검증 결과를 먼저 보여 주고, 확인을 누르면 반영. 오류는 시트·셀·고칠 방법으로 안내하고 기존 데이터는 유지</t>
+          <t>Vercel에 올릴 수 있는 구조로 정리</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10-14 13:10 · 19338d2</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>열람 권한: '명단 올리기'로 권한부여대상자 명단 업로드</t>
+          <t>동기화 확인 주기를 5분 단위로 설정</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10-14 13:46 · afc34cd</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>열람 권한: 대상자 이메일 확인(직접 수정 가능) 후 '연결'을 누르면 임시 비밀번호가 한 번만 표시됨. 잃어버리면 '재발급'</t>
+          <t>서버·로그인·윈도우 PC 폴더 동기화 추가</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10-14 13:50 · 2ba2f71</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>열람 권한: 공고마다 드롭다운에서 볼 사람을 '승인'. 명단은 후보만 제시하고 승인한 공고만 보임</t>
+          <t>동기화 기본 주기를 1시간으로 변경</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10-14 14:10 · 897d905</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>열람 권한: 완료 공고 표시 기간(0·7·14·30·60·90일) 변경</t>
+          <t>대상자 실명 선택 + 이메일 로그인, 완료 공고 표시 기간</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10-14 14:17 · 051ad5e</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>현업 화면 보기: 대상자를 고르면 그 사람 화면을 그대로 확인(보기 전용)</t>
+          <t>임시 비밀번호 자동 발급, 첫 로그인 비밀번호 변경, 완료 공고 기본 7일 표시</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10-14 14:41 · 96bee3f</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>기록: 동기화 이력과 권한 변경 이력</t>
+          <t>권한부여대상자 명단(이름·이메일) 따로 올리기, 명단 이메일 미리 채우기</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>10-14 15:12 · 4280f81</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>README: 재배포와 첫 관리자 로그인 안내</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>10-14 15:16 · 48e1194</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>저장소 연결 방식 확대(접두어 붙은 Upstash 변수, REDIS_URL), 설정 점검 /api/health, 실제 오류 문구 표시</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>10-14 15:50 · a1f5239</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>README: 기본 도메인으로 접속 안내</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>10-14 15:51 · 9a9fe06</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>설정 점검: 저장소 설정 이름과 실행 버전 표시</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>10-14 16:05 · bab2e4d</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>디자인 변경: 청록 사이드바 + 흰 카드 레이아웃, 로그인 첫 화면 개편</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>10-14 16:07 · 81dcea2</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>휴대폰 화면 요약 영역 다듬기</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>10-14 16:10 · 79e33a4</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>HR 관리자용 '현업 화면 보기' 메뉴 추가</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>10-14 16:14 · d7ba556</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>현업 화면 보기: 계정 연결 전에도 대상자 이름으로 미리보기</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>10-14 16:22 · 6bb30aa</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>열람 권한: 로그인 이메일 칸을 넓혀 전체 주소가 보이게</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>10-14 16:30 · d84eeb3</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>문서: 프로젝트 정리 (워드·엑셀) 추가</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>10-14 16:35 · d6ec6f9</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>화면 모션: 화면 전환 시 등장 효과, 막대 그래프 차오름, 숫자 카운트업, 호버·상세창 효과</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>10-14 16:40 · 521a088</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>화면 모션 강화: 로고 이퀄라이저, 떠다니는 배경 빛, 막대 숨쉬기·빛 반사, 진행 중 점 깜빡임, 행 강조선, 버튼 빛 효과</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>10-14 16:45 · b2c7e0c</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>화면 모션 완화: 반복되는 움직임 제거, 등장 효과와 마우스 반응만 유지</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>10-14 16:48 · 4b8f537</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>진행 중 표시의 점에 퍼지는 움직임 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>10-14 16:55 · 71b5321</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>테스트용 관리자 계정 test_admin 추가 (TEST_ADMIN_PASSWORD 환경 변수가 있을 때만 로그인 가능)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>10-14 17:08 · e6e8948</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>사용 편의 개선: 일괄 연결·승인, 임시 비밀번호 엑셀, 진행 막대·진행률, 그래프로 거르기, 로그인 편의, 모바일 가로 넘침 수정</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>10-14 17:12 · 83d199c</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>현재 단계 말풍선 모션 강조: 바깥으로 퍼지는 빛과 점 박동</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>10-14 17:13 · 6df9584</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>현재 단계 말풍선 바깥 빛 제거, 안쪽 점 박동만 유지</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>10-14 17:21 · 5061098</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>열람 권한: 권한부여 대상자 직접 추가·삭제 (명단 재업로드 후에도 유지)</t>
         </is>
       </c>
     </row>
@@ -837,11 +1180,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
     <col width="100" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -864,7 +1209,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>HR에게 받은 이메일과 임시 비밀번호로 로그인합니다.</t>
+          <t>로그인: 이메일 칸에 admin, 비밀번호 칸에 ADMIN_PASSWORD 값. 평가용은 test_admin / TEST_ADMIN_PASSWORD.</t>
         </is>
       </c>
     </row>
@@ -876,7 +1221,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>첫 로그인 때 8자 이상 새 비밀번호를 정해야 공고가 보입니다.</t>
+          <t>현황판: 전체 공고, 단계별 공고 수 그래프(막대를 누르면 그 단계 공고만 보기, 다시 누르거나 '전체 보기'로 해제), 공고별 진행 막대와 'N/9단계 처리'. 공고를 누르면 단계별 상세.</t>
         </is>
       </c>
     </row>
@@ -888,7 +1233,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>승인받은 공고의 단계별 상태(완료·진행 중·해당사항 없음)와 변경 이력을 봅니다.</t>
+          <t>엑셀 반영: 백데이터 엑셀을 올리면 검증 결과를 먼저 보여 주고 확인을 누르면 반영. 오류는 시트·셀·고칠 방법으로 안내하고 기존 데이터는 유지.</t>
         </is>
       </c>
     </row>
@@ -900,7 +1245,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>모든 단계가 끝난 공고는 7일 뒤 목록에서 사라집니다.</t>
+          <t>열람 권한 &gt; 한 번에 처리하기: ① 명단 이메일로 모두 연결(임시 비밀번호 자동 발급) → ② 같은 부서 후보 모두 승인. 공고마다 '후보 N명 모두 승인' 버튼도 있음.</t>
         </is>
       </c>
     </row>
@@ -912,7 +1257,67 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>비밀번호를 잊으면 HR에게 재발급을 요청합니다.</t>
+          <t>열람 권한 &gt; 임시 비밀번호: 이번에 발급한 목록을 '엑셀로 내려받기'(파일명 temp-passwords_날짜.xlsx). 화면을 벗어나면 다시 볼 수 없으니 바로 받기.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>열람 권한 &gt; 명단 올리기: '명단 파일 선택'으로 권한부여대상자 명단만 교체. 이미 연결한 계정과 승인은 유지.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>열람 권한 &gt; 대상자 직접 추가: 이름·이메일·소속 입력, '바로 연결' 체크 시 임시 비밀번호 발급. 직접 추가한 사람은 '삭제' 가능.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>열람 권한 &gt; 대상자 표: 이메일 직접 수정·저장, 연결 해제, 임시 비밀번호 재발급, 상태(첫 로그인 전/사용 중).</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>현업 화면 보기: 대상자를 골라 그 사람 화면을 그대로 확인(보기 전용).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>PC 자동 동기화·반영 기록: 동기화 주기 설정, 이력과 권한 변경 이력 확인.</t>
         </is>
       </c>
     </row>
@@ -927,11 +1332,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
     <col width="100" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -954,7 +1361,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>진행현황 시트와 프로세스 시트는 꼭 있어야 함. 권한부여대상자 시트는 있으면 반영, 없으면 기존 명단 유지</t>
+          <t>HR에게 받은 이메일과 임시 비밀번호로 로그인합니다. '보기'를 누르면 비밀번호를 확인하며 입력할 수 있고, '이메일 기억하기'를 켜면 다음에 이메일이 채워져 있습니다.</t>
         </is>
       </c>
     </row>
@@ -966,7 +1373,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>공고는 본부 + 부서 + 공고명으로 구분</t>
+          <t>첫 로그인 때 8자 이상 새 비밀번호를 정해야 공고가 보입니다.</t>
         </is>
       </c>
     </row>
@@ -978,7 +1385,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>파일에서 빠진 공고는 지우지 않고 '최근 파일에 없음'으로 표시</t>
+          <t>승인받은 공고의 현재 단계, 진행 막대(마우스를 올리면 단계 이름), 'N/9단계 처리'를 봅니다. 공고를 누르면 단계별 상세와 변경 이력이 나옵니다.</t>
         </is>
       </c>
     </row>
@@ -990,7 +1397,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>새 공고와 빠진 공고가 함께 있으면 PC 자동 동기화는 관리자 확인 전까지 반영을 멈춤</t>
+          <t>모든 단계가 끝난 공고는 7일 뒤 목록에서 사라집니다.</t>
         </is>
       </c>
     </row>
@@ -1002,43 +1409,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>마지막으로 반영한 파일보다 오래된 파일은 거절</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>같은 파일이 다시 오면 '정상 확인 시각'만 갱신</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>소속 정정: 재무기획부 → 경영기획본부, 계약관리부 → 손님지원본부</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>PC 동기화 확인 주기 기본 1시간, 5분 단위로 변경 가능</t>
+          <t>비밀번호를 잊으면 HR에게 임시 비밀번호 재발급을 요청합니다.</t>
         </is>
       </c>
     </row>
@@ -1056,8 +1427,10 @@
   <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
     <col width="100" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1080,7 +1453,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Vercel 환경 변수: ADMIN_PASSWORD, SESSION_SECRET, SYNC_KEY, UPSTASH_REDIS_REST_URL, UPSTASH_REDIS_REST_TOKEN (값은 Vercel에만 보관)</t>
+          <t>백데이터에는 채용현황(진행현황)·프로세스 시트가 꼭 있어야 함. 권한부여대상자 시트는 있으면 반영, 없으면 기존 명단 유지.</t>
         </is>
       </c>
     </row>
@@ -1092,7 +1465,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>값을 바꾼 뒤에는 Vercel 배포 화면에서 맨 위 배포의 ⋯ → 재배포(Redeploy)</t>
+          <t>공고는 본부 + 부서 + 공고명으로 구분. 파일에서 빠진 공고는 지우지 않고 '최근 파일에 없음'으로 표시.</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1477,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>GitHub 저장소는 공개라 실제 명단, 채용 데이터, 비밀번호와 토큰은 올리지 않음</t>
+          <t>새 공고와 빠진 공고가 함께 있으면(공고명 변경 의심) PC 자동 동기화는 관리자 확인 전까지 멈춤.</t>
         </is>
       </c>
     </row>
@@ -1116,7 +1489,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Upstash 토큰은 비밀번호와 같으니 채팅이나 메일에 붙여 넣지 않음</t>
+          <t>마지막으로 반영한 파일보다 오래된 파일은 거절. 같은 파일이 다시 오면 '정상 확인 시각'만 갱신.</t>
         </is>
       </c>
     </row>
@@ -1128,7 +1501,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>비밀번호는 암호화(scrypt)해서 저장, 로그인 정보는 서명된 쿠키로만 주고받음</t>
+          <t>후보 매칭: 공고의 본부·부서와 명단의 본부·부서 이름이 똑같아야 후보로 뜸. 소속 정정: 재무기획부 → 경영기획본부, 계약관리부 → 손님지원본부.</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1513,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>접속 주소는 d12l-hana06.vercel.app 사용 (git-main 주소는 예전 배포일 수 있음)</t>
+          <t>v.3 기준 후보 0명 공고: 계리리스크본부/리스크관리부(명단에 리스크관리부 없음), CEO 임원/소비자보호부(명단에는 '소비자보호관리책임자'만 있음). 해결: 명단에 그 부서 행 추가, 드롭다운 '그 외 대상자'에서 직접 승인, 또는 부서 이름을 맞춰 다시 올리기.</t>
         </is>
       </c>
     </row>
@@ -1155,94 +1528,108 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
     <col width="100" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>증상</t>
+          <t>번호</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>확인할 것</t>
+          <t>내용</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>로그인 후 서버 연결 오류</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>/api/health의 "저장소"가 "정상"인지. "없음"이면 Upstash 환경 변수 확인 후 재배포</t>
+          <t>환경 변수 값을 바꾸면 Vercel 배포 화면 맨 위 항목 ⋯ → 재배포(Redeploy).</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>환경 변수를 바꿨는데 그대로</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>재배포를 안 한 경우. 배포 화면 ⋯ → 재배포</t>
+          <t>코드를 바꾼 뒤에는 배포 상태가 Ready가 된 다음 사이트에서 Ctrl + F5로 새로고침.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>예전 화면이 보임</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>주소가 d12l-hana06.vercel.app인지 확인</t>
+          <t>GitHub 저장소는 공개라 실제 명단·채용 데이터·비밀번호·토큰은 올리지 않음.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>현업이 공고를 못 봄</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>연결 여부, 그 공고 승인 여부, 첫 비밀번호 변경 여부. '현업 화면 보기'로 같은 화면 확인</t>
+          <t>Upstash 토큰은 비밀번호와 같으니 채팅·메일에 붙여 넣지 않음.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>엑셀 반영 실패</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>안내된 시트·셀·고칠 방법대로 고치고 다시 업로드. 기존 데이터는 유지</t>
+          <t>비밀번호는 암호화(scrypt)해서 저장하고, 임시 비밀번호 원문은 서버에 남기지 않음.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>메뉴 이름이 이상함</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>브라우저 자동 번역 때문. Vercel 메뉴가 영어와 다를 수 있음</t>
+          <t>test_admin은 관리자와 권한이 같아 실제 데이터를 바꿀 수 있음. 평가가 끝나면 TEST_ADMIN_PASSWORD를 지우고 재배포.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>접속 주소는 d12l-hana06.vercel.app 사용 (git-main이 들어간 주소는 예전 배포일 수 있음).</t>
         </is>
       </c>
     </row>
@@ -1257,80 +1644,222 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
     <col width="100" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>번호</t>
+          <t>증상</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>내용</t>
+          <t>확인할 것</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>로그인 후 서버 연결 오류</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>운영 사이트 '열람 권한' 탭에 실제 명단 올리기</t>
+          <t>/api/health의 "저장소"가 "정상"인지. "없음"이면 Upstash 환경 변수 확인 후 재배포</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>바꾼 내용이 사이트에 안 보임</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>대상자별 이메일 확인 후 '연결', 임시 비밀번호 전달</t>
+          <t>배포가 Ready인지 확인 후 Ctrl + F5</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>환경 변수를 바꿨는데 그대로</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>공고별 '승인'</t>
+          <t>재배포를 안 한 경우. 배포 화면 ⋯ → 재배포</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>현업이 공고를 못 봄</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>회사 윈도우 PC에 동기화 프로그램 설치(agent 폴더의 설치.bat, 실제 PC에서는 아직 시험 전)</t>
+          <t>계정 연결, 그 공고 승인, 첫 비밀번호 변경 여부. '현업 화면 보기'로 같은 화면 확인</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>일괄 승인 후에도 후보 0명 공고</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>명단에 같은 본부·부서가 없음. 드롭다운에서 직접 승인하거나 명단 수정</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>일괄 연결에서 빠진 사람</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>같은 이메일이 다른 사람에게 이미 연결됨. '연결하지 못한 대상자' 안내 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>엑셀 반영 실패</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>안내된 시트·셀·고칠 방법대로 고친 뒤 다시 업로드</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="100" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>번호</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>내용</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>운영 사이트에 백데이터 v.3 올리기(엑셀 반영 탭) — 공고와 명단이 함께 바뀜</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>열람 권한 &gt; 한 번에 처리하기: ① 모두 연결 → 임시 비밀번호 엑셀 받기 → ② 후보 모두 승인</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>후보 0명 공고 2건(리스크관리부, 소비자보호부) 볼 사람 정해서 승인</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>임시 비밀번호를 대상자에게 전달</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>평가가 끝나면 TEST_ADMIN_PASSWORD 삭제 후 재배포</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>회사 윈도우 PC에 동기화 프로그램 설치(GitHub agent 폴더의 설치.bat, 실제 PC에서는 아직 시험 전)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>회사의 외부 클라우드 저장 허용 여부 확인</t>
         </is>
